--- a/tech_ARC_simple.xlsx
+++ b/tech_ARC_simple.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hravoaha\Desktop\Thèse\Thèse 2023\Objectif 2\biowaste_optim\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01055CAA-3379-450D-9BBA-8BC980F6E315}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E223C5D4-6BA1-4F3E-A89D-2313B1B24A5C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6930" xr2:uid="{D746D7D5-B0A8-4858-AD5A-93AA09E65399}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6930" activeTab="3" xr2:uid="{D746D7D5-B0A8-4858-AD5A-93AA09E65399}"/>
   </bookViews>
   <sheets>
     <sheet name="id_tech" sheetId="2" r:id="rId1"/>
@@ -240,7 +240,7 @@
       </sheetData>
       <sheetData sheetId="2" refreshError="1"/>
       <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4"/>
+      <sheetData sheetId="4" refreshError="1"/>
       <sheetData sheetId="5" refreshError="1"/>
       <sheetData sheetId="6" refreshError="1"/>
       <sheetData sheetId="7" refreshError="1"/>
@@ -248,20 +248,8 @@
       <sheetData sheetId="9" refreshError="1"/>
       <sheetData sheetId="10" refreshError="1"/>
       <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12">
-        <row r="21">
-          <cell r="C21">
-            <v>2.0114159106083146E-8</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="13">
-        <row r="21">
-          <cell r="C21">
-            <v>9.4856034682359522E-2</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
